--- a/data/gravel/Enigma Escape Mk.III 2025.xlsx
+++ b/data/gravel/Enigma Escape Mk.III 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA22FBA4-5D95-2B42-B405-DD90BE0FC988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079846E6-988A-B844-83FA-4B450BD6F348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25760" yWindow="-19480" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3440" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>external</t>
+  </si>
+  <si>
+    <t>https://www.enigmabikes.com/cdn/shop/files/Enigma-Escape--Hero_2500x.jpg?v=1752244017</t>
   </si>
 </sst>
 </file>
@@ -759,6 +762,11 @@
         <v>96</v>
       </c>
     </row>
+    <row r="6" spans="1:23">
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Enigma Escape Mk.III 2025.xlsx
+++ b/data/gravel/Enigma Escape Mk.III 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079846E6-988A-B844-83FA-4B450BD6F348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC98E4FE-9E46-1E40-A3EB-F90DD9A6E19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -287,9 +287,6 @@
     <t>a8:f34</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>gravel</t>
   </si>
   <si>
@@ -345,6 +342,15 @@
   </si>
   <si>
     <t>https://www.enigmabikes.com/cdn/shop/files/Enigma-Escape--Hero_2500x.jpg?v=1752244017</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Hailsham, East Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -716,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -735,7 +741,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -759,12 +765,12 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -780,7 +786,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" s="5">
         <v>50</v>
@@ -801,16 +807,16 @@
         <v>60</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>14</v>
@@ -819,22 +825,22 @@
         <v>16</v>
       </c>
       <c r="P8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="R8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>24</v>
@@ -848,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="5">
         <v>500</v>
@@ -984,7 +990,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="5">
         <v>115</v>
@@ -1188,7 +1194,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C14" s="5">
         <v>76</v>
@@ -1256,7 +1262,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C15" s="5">
         <v>70</v>
@@ -1282,7 +1288,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="5">
         <v>50</v>
@@ -1308,7 +1314,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="5">
         <v>551</v>
@@ -1334,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="5">
         <v>360</v>
@@ -1360,7 +1366,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19" s="5">
         <v>1005</v>
@@ -1478,7 +1484,7 @@
         <v>395</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1669,7 +1675,7 @@
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1677,7 +1683,7 @@
         <v>80</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1690,7 +1696,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1784,7 +1790,7 @@
         <v>57</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1823,7 +1829,7 @@
         <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1837,7 +1843,7 @@
         <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1930,7 +1936,15 @@
         <v>77</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Enigma Escape Mk.III 2025.xlsx
+++ b/data/gravel/Enigma Escape Mk.III 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC98E4FE-9E46-1E40-A3EB-F90DD9A6E19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77122202-8878-5A41-9C45-8D002CD9D287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>Hailsham, East Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -722,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1766,166 +1784,148 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53">
-        <v>31.6</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>54</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58">
-        <v>140</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>72</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>44</v>
+        <v>67</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B71">
-        <v>2199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72">
-        <v>4290</v>
+        <v>69</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>44</v>
@@ -1933,17 +1933,65 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
         <v>104</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>105</v>
       </c>
     </row>
